--- a/data/Class.xlsx
+++ b/data/Class.xlsx
@@ -475,13 +475,10 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>1101</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>13</v>
+        <v>1106</v>
       </c>
       <c r="E6" t="n">
         <v>500</v>
@@ -510,13 +507,10 @@
         <v>2</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>1201</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
+        <v>1206</v>
       </c>
       <c r="E7" t="n">
         <v>500</v>
@@ -545,13 +539,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1301</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
+        <v>1306</v>
       </c>
       <c r="E8" t="n">
         <v>500</v>
@@ -580,13 +571,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>1401</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
+        <v>1406</v>
       </c>
       <c r="E9" t="n">
         <v>500</v>
